--- a/app/reports/GROW_research.xlsx
+++ b/app/reports/GROW_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-05 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-08 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04532000064849853</v>
+        <v>0.04552000045776367</v>
       </c>
     </row>
     <row r="6">
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="8">
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>33772000</v>
+        <v>34733000</v>
       </c>
     </row>
     <row r="34">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>12404195.65217391</v>
+        <v>12404196.3898917</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="38">
@@ -1493,16 +1493,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>34235580</v>
+        <v>34359624</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>11.04</v>
+        <v>11.08</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>-0</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="6">
@@ -1517,14 +1517,14 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>1279059328</v>
+        <v>1241021696</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n">
-        <v>-2559.8</v>
+        <v>-2348.896</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>252.206</v>
+        <v>231.427</v>
       </c>
     </row>
     <row r="7">
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>25803552</v>
+        <v>26728110</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>17.055555</v>
+        <v>17.666666</v>
       </c>
       <c r="E7" s="33" t="n"/>
       <c r="F7" s="33" t="n">
@@ -1597,12 +1597,12 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>17174642</v>
+        <v>17535454</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="33" t="n">
-        <v>7.405</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="11">
@@ -1617,14 +1617,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>37926700</v>
+        <v>38533200</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>27.588236</v>
+        <v>28.029411</v>
       </c>
       <c r="E11" s="33" t="n"/>
       <c r="F11" s="33" t="n">
-        <v>5.83</v>
+        <v>6.097</v>
       </c>
     </row>
     <row r="12">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C12" s="32" t="n"/>
       <c r="D12" s="33" t="n">
-        <v>29.682539</v>
+        <v>29.500626</v>
       </c>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="33" t="n"/>

--- a/app/reports/GROW_research.xlsx
+++ b/app/reports/GROW_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-08 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-09 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2.77</v>
+        <v>2.7501</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.04532000064849853</v>
       </c>
     </row>
     <row r="6">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>12404196.3898917</v>
+        <v>12404196.21104687</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>2.77</v>
+        <v>2.7501</v>
       </c>
     </row>
     <row r="38">
@@ -1493,16 +1493,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>34359624</v>
+        <v>34112780</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>11.08</v>
+        <v>11</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="6">
@@ -1517,14 +1517,14 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>1241021696</v>
+        <v>1207867136</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n">
-        <v>-2348.896</v>
+        <v>-772.977</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>231.427</v>
+        <v>76.158</v>
       </c>
     </row>
     <row r="7">
@@ -1539,14 +1539,14 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>26728110</v>
+        <v>27052546</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>17.666666</v>
+        <v>17.881111</v>
       </c>
       <c r="E7" s="33" t="n"/>
       <c r="F7" s="33" t="n">
-        <v>0.317</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="8">
@@ -1577,12 +1577,12 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>19134374</v>
+        <v>18855040</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n"/>
       <c r="F9" s="33" t="n">
-        <v>15.723</v>
+        <v>15.206</v>
       </c>
     </row>
     <row r="10">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>17535454</v>
+        <v>16885992</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n"/>
@@ -1617,14 +1617,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>38533200</v>
+        <v>38856668</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>28.029411</v>
+        <v>28.264704</v>
       </c>
       <c r="E11" s="33" t="n"/>
       <c r="F11" s="33" t="n">
-        <v>6.097</v>
+        <v>6.091</v>
       </c>
     </row>
     <row r="12">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C12" s="32" t="n"/>
       <c r="D12" s="33" t="n">
-        <v>29.500626</v>
+        <v>29.109797</v>
       </c>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="33" t="n"/>

--- a/app/reports/GROW_research.xlsx
+++ b/app/reports/GROW_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-09 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-10 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2.7501</v>
+        <v>2.82</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04532000064849853</v>
+        <v>0.04547999858856201</v>
       </c>
     </row>
     <row r="6">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>12404196.21104687</v>
+        <v>12404195.74468085</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>2.7501</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="38">
@@ -1493,16 +1493,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>34112780</v>
+        <v>34979832</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>11</v>
+        <v>11.28</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>0.4</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="6">
@@ -1517,14 +1517,14 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>1207867136</v>
+        <v>1187563264</v>
       </c>
       <c r="D6" s="33" t="n"/>
       <c r="E6" s="33" t="n">
-        <v>-772.977</v>
+        <v>-808.128</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>76.158</v>
+        <v>79.621</v>
       </c>
     </row>
     <row r="7">
@@ -1539,14 +1539,14 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>27052546</v>
+        <v>26391908</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>17.881111</v>
+        <v>17.444445</v>
       </c>
       <c r="E7" s="33" t="n"/>
       <c r="F7" s="33" t="n">
-        <v>0.325</v>
+        <v>0.321</v>
       </c>
     </row>
     <row r="8">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>18855040</v>
+        <v>17896924</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n"/>
@@ -1597,12 +1597,12 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>16885992</v>
+        <v>17824104</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="33" t="n">
-        <v>7.4</v>
+        <v>7.392</v>
       </c>
     </row>
     <row r="11">
@@ -1617,14 +1617,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>38856668</v>
+        <v>37523172</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>28.264704</v>
+        <v>27.294706</v>
       </c>
       <c r="E11" s="33" t="n"/>
       <c r="F11" s="33" t="n">
-        <v>6.091</v>
+        <v>6.001</v>
       </c>
     </row>
     <row r="12">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C12" s="32" t="n"/>
       <c r="D12" s="33" t="n">
-        <v>29.109797</v>
+        <v>29.164345</v>
       </c>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="33" t="n"/>
